--- a/tame_output/ON/bt/strategyON_20231117.xlsx
+++ b/tame_output/ON/bt/strategyON_20231117.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>88.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>103.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.7%</t>
+          <t>133.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1783"/>
+  <dimension ref="A1:G1784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.14701126014534</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42535,6 +42535,29 @@
       </c>
       <c r="G1783" t="n">
         <v>4.399803392038762</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="B1784" t="n">
+        <v>3.120622377288061</v>
+      </c>
+      <c r="C1784" t="n">
+        <v>3.089704189836242</v>
+      </c>
+      <c r="D1784" t="n">
+        <v>1.555140714168145</v>
+      </c>
+      <c r="E1784" t="n">
+        <v>3.711404051189753</v>
+      </c>
+      <c r="F1784" t="n">
+        <v>2.178386801284801</v>
+      </c>
+      <c r="G1784" t="n">
+        <v>4.396736270607124</v>
       </c>
     </row>
   </sheetData>
